--- a/Draft_Methodology_Azure_FINAL.xlsx
+++ b/Draft_Methodology_Azure_FINAL.xlsx
@@ -675,7 +675,13 @@
 # Optional: node index.js --config config/azure.js --compliance=cis1</s:t>
         </s:is>
       </s:c>
-      <s:c r="J6" s="1" t="n"/>
+      <s:c r="J6" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1580 - Cloud Infrastructure Discovery
+T1526 - Cloud Service Discovery
+T1595.002 - Vulnerability Scanning</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K6" s="1" t="n"/>
       <s:c r="L6" s="1" t="n"/>
       <s:c r="M6" s="1" t="inlineStr">
@@ -785,7 +791,12 @@
           <s:t>az ad user list --query "[?userType=='Guest'] | length(@) == `0` || 'Non-compliant: Guest users detected' || 'Compliant: No guest users detected'"</s:t>
         </s:is>
       </s:c>
-      <s:c r="J9" s="1" t="n"/>
+      <s:c r="J9" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1087.004 - Cloud Account
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K9" s="1" t="n"/>
       <s:c r="L9" s="1" t="n"/>
       <s:c r="M9" s="1" t="inlineStr">
@@ -833,7 +844,12 @@
           <s:t>az rest --method get --url https://graph.microsoft.com/v1.0/policies/authorizationPolicy | jq '.defaultUserRolePermissions.allowedToCreateTenants | if . == true then "Non-compliant: Unrestricted Tenant Creation by Non-Admin Users in Microsoft Entra ID" else "Compliant: Tenant creation restricted to admins" end'</s:t>
         </s:is>
       </s:c>
-      <s:c r="J10" s="1" t="n"/>
+      <s:c r="J10" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1136.003 - Cloud Account
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K10" s="1" t="n"/>
       <s:c r="L10" s="1" t="n"/>
       <s:c r="M10" s="1" t="inlineStr">
@@ -880,7 +896,12 @@
           <s:t>Azure Portal → Microsoft Entra ID → Manage → Properties → Manage Security Defaults → Enable Security Defaults</s:t>
         </s:is>
       </s:c>
-      <s:c r="J11" s="1" t="n"/>
+      <s:c r="J11" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1556.006 - Multi-Factor Authentication
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K11" s="1" t="n"/>
       <s:c r="L11" s="1" t="n"/>
       <s:c r="M11" s="1" t="inlineStr">
@@ -927,7 +948,12 @@
           <s:t>Azure Portal → Microsoft Entra ID → Users → User Settings → Manage External Collaboration Settings → Guest user permissions are limited</s:t>
         </s:is>
       </s:c>
-      <s:c r="J12" s="1" t="n"/>
+      <s:c r="J12" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K12" s="1" t="n"/>
       <s:c r="L12" s="1" t="n"/>
       <s:c r="M12" s="1" t="inlineStr">
@@ -975,7 +1001,12 @@
           <s:t>az ad user list --query "[?strongAuthenticationMethods==null].userPrincipalName" --output json | jq 'if length == 0 then "Compliant: All users have Multi-Factor Authentication enabled" else "Non-Compliant: Insufficient Multi-Factor Authentication Coverage for User Accounts" end'</s:t>
         </s:is>
       </s:c>
-      <s:c r="J13" s="1" t="n"/>
+      <s:c r="J13" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1556.006 - Multi-Factor Authentication
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K13" s="1" t="n"/>
       <s:c r="L13" s="1" t="n"/>
       <s:c r="M13" s="1" t="inlineStr">
@@ -1025,7 +1056,12 @@
 prowler azure --check entra_security_defaults_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J14" s="1" t="n"/>
+      <s:c r="J14" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1556.006 - Multi-Factor Authentication
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K14" s="1" t="n"/>
       <s:c r="L14" s="1" t="n"/>
       <s:c r="M14" s="1" t="inlineStr">
@@ -1072,7 +1108,12 @@
           <s:t>Azure Portal → Microsoft Entra ID → Users → User Settings → Administration Portal → Restrict access to Microsoft Entra ID administration portal</s:t>
         </s:is>
       </s:c>
-      <s:c r="J15" s="1" t="n"/>
+      <s:c r="J15" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1538 - Cloud Service Dashboard</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K15" s="1" t="n"/>
       <s:c r="L15" s="1" t="n"/>
       <s:c r="M15" s="1" t="inlineStr">
@@ -1122,7 +1163,12 @@
 echo "Unrestricted Guest User Access"</s:t>
         </s:is>
       </s:c>
-      <s:c r="J16" s="1" t="n"/>
+      <s:c r="J16" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K16" s="1" t="n"/>
       <s:c r="L16" s="1" t="n"/>
       <s:c r="M16" s="1" t="inlineStr">
@@ -1172,7 +1218,12 @@
 echo "Compliant: User consent to third-party applications is restricted"</s:t>
         </s:is>
       </s:c>
-      <s:c r="J17" s="1" t="n"/>
+      <s:c r="J17" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1528 - Steal Application Access Token
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K17" s="1" t="n"/>
       <s:c r="L17" s="1" t="n"/>
       <s:c r="M17" s="1" t="inlineStr">
@@ -1219,7 +1270,12 @@
           <s:t>Azure Portal → Microsoft Entra ID → Users → User Settings → App Registrations → Users can register applications</s:t>
         </s:is>
       </s:c>
-      <s:c r="J18" s="1" t="n"/>
+      <s:c r="J18" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1136.003 - Cloud Account</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K18" s="1" t="n"/>
       <s:c r="L18" s="1" t="n"/>
       <s:c r="M18" s="1" t="inlineStr">
@@ -1266,7 +1322,12 @@
           <s:t>prowler azure --az-cli-auth --subscription-ids &lt;subscription-id&gt; --compliance cis_5.0_azure  # requirement 5.3.2</s:t>
         </s:is>
       </s:c>
-      <s:c r="J19" s="1" t="n"/>
+      <s:c r="J19" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1087.004 - Cloud Account
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K19" s="1" t="n"/>
       <s:c r="L19" s="1" t="n"/>
       <s:c r="M19" s="1" t="n"/>
@@ -1328,7 +1389,12 @@
           <s:t>Locate the Shared Access Signature (SAS) token defined within the SAS URL provided to your storage account clients. The SAS token starts with a question mark, followed by a set of various parameters, e.g. ?sv=2018-03-28&amp;ss=bfqt&amp;srt=sco&amp;sp=rwdlacup&amp;se=2019-06-11T10:25:43Z&amp;st=2019-06-11T11:25:43Z &amp;spr=https,http&amp;sig=abcdabcdabcdabcdabcdabcdabcdabcdabcdabcdabcdabcd. Identify the communication protocol used for the verified token, defined as value for the spr parameter, for example spr=https,http. If the spr parameter is not set to HTTPS only (i.e. spr=https), the selected Shared Access Signature (SAS) token's configuration is not compliant.</s:t>
         </s:is>
       </s:c>
-      <s:c r="J21" s="1" t="n"/>
+      <s:c r="J21" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1530 - Data from Cloud Storage
+T1048.003 - Exfiltration Over Unencrypted Non-C2 Protocol</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K21" s="1" t="n"/>
       <s:c r="L21" s="1" t="n"/>
       <s:c r="M21" s="1" t="inlineStr">
@@ -1386,7 +1452,12 @@
 ``</s:t>
         </s:is>
       </s:c>
-      <s:c r="J22" s="1" t="n"/>
+      <s:c r="J22" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1530 - Data from Cloud Storage
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K22" s="1" t="n"/>
       <s:c r="L22" s="1" t="n"/>
       <s:c r="M22" s="1" t="inlineStr">
@@ -1441,7 +1512,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J23" s="1" t="n"/>
+      <s:c r="J23" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1530 - Data from Cloud Storage
+T1048.003 - Exfiltration Over Unencrypted Non-C2 Protocol</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K23" s="1" t="n"/>
       <s:c r="L23" s="1" t="n"/>
       <s:c r="M23" s="1" t="inlineStr">
@@ -1497,7 +1573,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J24" s="1" t="n"/>
+      <s:c r="J24" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1530 - Data from Cloud Storage
+T1590.005 - IP Addresses</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K24" s="1" t="n"/>
       <s:c r="L24" s="1" t="n"/>
       <s:c r="M24" s="1" t="inlineStr">
@@ -1544,7 +1625,12 @@
           <s:t>prowler azure --check storage_default_to_entra_authorization_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J25" s="1" t="n"/>
+      <s:c r="J25" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1556.006 - Multi-Factor Authentication</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K25" s="1" t="n"/>
       <s:c r="L25" s="1" t="n"/>
       <s:c r="M25" s="1" t="inlineStr">
@@ -1611,7 +1697,12 @@
 az cognitiveservices account show -n &lt;name&gt; -g &lt;rg&gt; --query properties.publicNetworkAccess</s:t>
         </s:is>
       </s:c>
-      <s:c r="J27" s="1" t="n"/>
+      <s:c r="J27" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K27" s="1" t="n"/>
       <s:c r="L27" s="1" t="n"/>
       <s:c r="M27" s="1" t="inlineStr">
@@ -1688,7 +1779,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J29" s="1" t="n"/>
+      <s:c r="J29" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1210 - Exploitation of Remote Services
+T1021.006 - Windows Remote Management</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K29" s="1" t="n"/>
       <s:c r="L29" s="1" t="n"/>
       <s:c r="M29" s="1" t="inlineStr">
@@ -1745,7 +1841,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J30" s="1" t="n"/>
+      <s:c r="J30" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1648 - Serverless Execution</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K30" s="1" t="n"/>
       <s:c r="L30" s="1" t="n"/>
       <s:c r="M30" s="1" t="inlineStr">
@@ -1803,7 +1904,12 @@
 ``</s:t>
         </s:is>
       </s:c>
-      <s:c r="J31" s="1" t="n"/>
+      <s:c r="J31" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1552.005 - Cloud Instance Metadata API</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K31" s="1" t="n"/>
       <s:c r="L31" s="1" t="n"/>
       <s:c r="M31" s="1" t="inlineStr">
@@ -1882,7 +1988,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J33" s="1" t="n"/>
+      <s:c r="J33" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.001 - Disable or Modify Tools
+T1518.001 - Security Software Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K33" s="1" t="n"/>
       <s:c r="L33" s="1" t="n"/>
       <s:c r="M33" s="1" t="inlineStr">
@@ -1943,7 +2054,12 @@
 done</s:t>
         </s:is>
       </s:c>
-      <s:c r="J34" s="1" t="n"/>
+      <s:c r="J34" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K34" s="1" t="n"/>
       <s:c r="L34" s="1" t="n"/>
       <s:c r="M34" s="1" t="inlineStr">
@@ -2009,7 +2125,12 @@
           <s:t>az network nsg rule list --nsg-name &lt;nsg&gt; -g &lt;rg&gt; -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J36" s="1" t="n"/>
+      <s:c r="J36" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1046 - Network Service Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K36" s="1" t="n"/>
       <s:c r="L36" s="1" t="n"/>
       <s:c r="M36" s="1" t="inlineStr">
@@ -2056,7 +2177,12 @@
           <s:t>prowler azure --check network_flow_log_more_than_90_days,network_bastion_host_exists</s:t>
         </s:is>
       </s:c>
-      <s:c r="J37" s="1" t="n"/>
+      <s:c r="J37" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1040 - Network Sniffing
+T1049 - System Network Connections Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K37" s="1" t="n"/>
       <s:c r="L37" s="1" t="n"/>
       <s:c r="M37" s="1" t="inlineStr">
@@ -2104,7 +2230,12 @@
 prowler azure --check network_nic_ip_forwarding_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J38" s="1" t="n"/>
+      <s:c r="J38" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1090.001 - Internal Proxy
+T1049 - System Network Connections Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K38" s="1" t="n"/>
       <s:c r="L38" s="1" t="n"/>
       <s:c r="M38" s="1" t="inlineStr">
@@ -2171,7 +2302,12 @@
 prowler azure --check aks_clusters_public_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J40" s="1" t="n"/>
+      <s:c r="J40" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1613 - Container and Resource Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K40" s="1" t="n"/>
       <s:c r="L40" s="1" t="n"/>
       <s:c r="M40" s="1" t="inlineStr">
@@ -2219,7 +2355,12 @@
 prowler azure --check aks_clusters_created_with_private_nodes</s:t>
         </s:is>
       </s:c>
-      <s:c r="J41" s="1" t="n"/>
+      <s:c r="J41" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1613 - Container and Resource Discovery
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K41" s="1" t="n"/>
       <s:c r="L41" s="1" t="n"/>
       <s:c r="M41" s="1" t="inlineStr">
@@ -2267,7 +2408,12 @@
 prowler azure --check aks_cluster_rbac_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J42" s="1" t="n"/>
+      <s:c r="J42" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1098.006 - Additional Container Cluster Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K42" s="1" t="n"/>
       <s:c r="L42" s="1" t="n"/>
       <s:c r="M42" s="1" t="inlineStr">
@@ -2334,7 +2480,12 @@
 prowler azure --check apim_threat_detection_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J44" s="1" t="n"/>
+      <s:c r="J44" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1040 - Network Sniffing</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K44" s="1" t="n"/>
       <s:c r="L44" s="1" t="n"/>
       <s:c r="M44" s="1" t="inlineStr">
@@ -2382,7 +2533,12 @@
 prowler azure --check apim_public_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J45" s="1" t="n"/>
+      <s:c r="J45" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K45" s="1" t="n"/>
       <s:c r="L45" s="1" t="n"/>
       <s:c r="M45" s="1" t="inlineStr">
@@ -2448,7 +2604,12 @@
           <s:t>az role definition list --custom-role-only true --query "[?contains(roleName,'Owner')]" -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J47" s="1" t="n"/>
+      <s:c r="J47" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K47" s="1" t="n"/>
       <s:c r="L47" s="1" t="n"/>
       <s:c r="M47" s="1" t="inlineStr">
@@ -2495,7 +2656,12 @@
           <s:t>az role definition list --custom-role-only true -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J48" s="1" t="n"/>
+      <s:c r="J48" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K48" s="1" t="n"/>
       <s:c r="L48" s="1" t="n"/>
       <s:c r="M48" s="1" t="inlineStr">
@@ -2561,7 +2727,12 @@
           <s:t>prowler azure --check monitor_alert_create_policy_assignment,monitor_alert_create_update_nsg,monitor_alert_create_update_public_ip_address_rule</s:t>
         </s:is>
       </s:c>
-      <s:c r="J50" s="1" t="n"/>
+      <s:c r="J50" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.008 - Disable or Modify Cloud Logs
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K50" s="1" t="n"/>
       <s:c r="L50" s="1" t="n"/>
       <s:c r="M50" s="1" t="inlineStr">
@@ -2609,7 +2780,12 @@
 prowler azure --check monitor_alert_service_health_advisory</s:t>
         </s:is>
       </s:c>
-      <s:c r="J51" s="1" t="n"/>
+      <s:c r="J51" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.008 - Disable or Modify Cloud Logs
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K51" s="1" t="n"/>
       <s:c r="L51" s="1" t="n"/>
       <s:c r="M51" s="1" t="inlineStr">
@@ -2675,7 +2851,12 @@
           <s:t>az advisor recommendation list --category Security --query "[].{resource:resourceMetadata.resourceId, rec:shortDescription.problem}" -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J53" s="1" t="n"/>
+      <s:c r="J53" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1580 - Cloud Infrastructure Discovery
+T1526 - Cloud Service Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K53" s="1" t="n"/>
       <s:c r="L53" s="1" t="n"/>
       <s:c r="M53" s="1" t="inlineStr">
@@ -2742,7 +2923,12 @@
 prowler azure --check app_remote_debugging_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J55" s="1" t="n"/>
+      <s:c r="J55" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1210 - Exploitation of Remote Services
+T1021.006 - Windows Remote Management</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K55" s="1" t="n"/>
       <s:c r="L55" s="1" t="n"/>
       <s:c r="M55" s="1" t="inlineStr">
@@ -2790,7 +2976,12 @@
 prowler azure --check app_key_vault_reference_identity</s:t>
         </s:is>
       </s:c>
-      <s:c r="J56" s="1" t="n"/>
+      <s:c r="J56" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1555 - Credentials from Password Stores
+T1552.001 - Credentials In Files</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K56" s="1" t="n"/>
       <s:c r="L56" s="1" t="n"/>
       <s:c r="M56" s="1" t="inlineStr">
@@ -2838,7 +3029,12 @@
 prowler azure --check app_ensure_auth_is_set_up</s:t>
         </s:is>
       </s:c>
-      <s:c r="J57" s="1" t="n"/>
+      <s:c r="J57" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1556.006 - Multi-Factor Authentication</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K57" s="1" t="n"/>
       <s:c r="L57" s="1" t="n"/>
       <s:c r="M57" s="1" t="inlineStr">
@@ -2905,7 +3101,12 @@
 prowler azure --check containerapp_environment_public_network_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J59" s="1" t="n"/>
+      <s:c r="J59" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K59" s="1" t="n"/>
       <s:c r="L59" s="1" t="n"/>
       <s:c r="M59" s="1" t="inlineStr">
@@ -2953,7 +3154,12 @@
 prowler azure --check containerapp_managed_identity_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J60" s="1" t="n"/>
+      <s:c r="J60" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1552.005 - Cloud Instance Metadata API</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K60" s="1" t="n"/>
       <s:c r="L60" s="1" t="n"/>
       <s:c r="M60" s="1" t="inlineStr">
@@ -3020,7 +3226,12 @@
 prowler azure --check containerapp_environment_public_network_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J62" s="1" t="n"/>
+      <s:c r="J62" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1610 - Deploy Container</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K62" s="1" t="n"/>
       <s:c r="L62" s="1" t="n"/>
       <s:c r="M62" s="1" t="inlineStr">
@@ -3068,7 +3279,12 @@
 prowler azure --check acr_private_endpoint_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J63" s="1" t="n"/>
+      <s:c r="J63" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1610 - Deploy Container</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K63" s="1" t="n"/>
       <s:c r="L63" s="1" t="n"/>
       <s:c r="M63" s="1" t="inlineStr">
@@ -3135,7 +3351,12 @@
 prowler azure --check databricks_workspace_vnet_injection_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J65" s="1" t="n"/>
+      <s:c r="J65" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1580 - Cloud Infrastructure Discovery
+T1016 - System Network Configuration Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K65" s="1" t="n"/>
       <s:c r="L65" s="1" t="n"/>
       <s:c r="M65" s="1" t="inlineStr">
@@ -3202,7 +3423,12 @@
 prowler azure --check frontdoor_waf_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J67" s="1" t="n"/>
+      <s:c r="J67" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1562.007 - Disable or Modify Cloud Firewall</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K67" s="1" t="n"/>
       <s:c r="L67" s="1" t="n"/>
       <s:c r="M67" s="1" t="inlineStr">
@@ -3250,7 +3476,12 @@
 prowler azure --check frontdoor_minimum_tls_version_enforced</s:t>
         </s:is>
       </s:c>
-      <s:c r="J68" s="1" t="n"/>
+      <s:c r="J68" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1040 - Network Sniffing</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K68" s="1" t="n"/>
       <s:c r="L68" s="1" t="n"/>
       <s:c r="M68" s="1" t="inlineStr">
@@ -3317,7 +3548,12 @@
 prowler azure --check keyvault_rbac_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J70" s="1" t="n"/>
+      <s:c r="J70" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1555 - Credentials from Password Stores</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K70" s="1" t="n"/>
       <s:c r="L70" s="1" t="n"/>
       <s:c r="M70" s="1" t="inlineStr">
@@ -3365,7 +3601,12 @@
 prowler azure --check keyvault_recoverable_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J71" s="1" t="n"/>
+      <s:c r="J71" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1490 - Inhibit System Recovery
+T1485 - Data Destruction</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K71" s="1" t="n"/>
       <s:c r="L71" s="1" t="n"/>
       <s:c r="M71" s="1" t="inlineStr">
@@ -3413,7 +3654,12 @@
 prowler azure --check keyvault_firewall_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J72" s="1" t="n"/>
+      <s:c r="J72" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1555 - Credentials from Password Stores
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K72" s="1" t="n"/>
       <s:c r="L72" s="1" t="n"/>
       <s:c r="M72" s="1" t="inlineStr">
@@ -3461,7 +3707,12 @@
 prowler azure --check keyvault_private_endpoint_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J73" s="1" t="n"/>
+      <s:c r="J73" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1555 - Credentials from Password Stores
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K73" s="1" t="n"/>
       <s:c r="L73" s="1" t="n"/>
       <s:c r="M73" s="1" t="inlineStr">
@@ -3508,7 +3759,12 @@
           <s:t>prowler azure --check keyvault_purge_protection_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J74" s="1" t="n"/>
+      <s:c r="J74" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1485 - Data Destruction
+T1490 - Inhibit System Recovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K74" s="1" t="n"/>
       <s:c r="L74" s="1" t="n"/>
       <s:c r="M74" s="1" t="inlineStr">
@@ -3575,7 +3831,12 @@
 prowler azure --check locks_resource_locked</s:t>
         </s:is>
       </s:c>
-      <s:c r="J76" s="1" t="n"/>
+      <s:c r="J76" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1484 - Domain or Tenant Policy Modification
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K76" s="1" t="n"/>
       <s:c r="L76" s="1" t="n"/>
       <s:c r="M76" s="1" t="inlineStr">
@@ -3642,7 +3903,12 @@
 prowler azure --check ml_workspace_encrypted_with_cmk</s:t>
         </s:is>
       </s:c>
-      <s:c r="J78" s="1" t="n"/>
+      <s:c r="J78" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1486 - Data Encrypted for Impact
+T1600 - Weaken Encryption</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K78" s="1" t="n"/>
       <s:c r="L78" s="1" t="n"/>
       <s:c r="M78" s="1" t="inlineStr">
@@ -3709,7 +3975,12 @@
 prowler azure --check monitor_diagnostic_settings_exists</s:t>
         </s:is>
       </s:c>
-      <s:c r="J80" s="1" t="n"/>
+      <s:c r="J80" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.008 - Disable or Modify Cloud Logs
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K80" s="1" t="n"/>
       <s:c r="L80" s="1" t="n"/>
       <s:c r="M80" s="1" t="inlineStr">
@@ -3757,7 +4028,12 @@
 prowler azure --check monitor_diagnostic_setting_subscription_activity_log</s:t>
         </s:is>
       </s:c>
-      <s:c r="J81" s="1" t="n"/>
+      <s:c r="J81" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.008 - Disable or Modify Cloud Logs
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K81" s="1" t="n"/>
       <s:c r="L81" s="1" t="n"/>
       <s:c r="M81" s="1" t="inlineStr">
@@ -3824,7 +4100,12 @@
 prowler azure --check mysql_flexible_server_ssl_connection_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J83" s="1" t="n"/>
+      <s:c r="J83" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1040 - Network Sniffing
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K83" s="1" t="n"/>
       <s:c r="L83" s="1" t="n"/>
       <s:c r="M83" s="1" t="inlineStr">
@@ -3891,7 +4172,12 @@
 prowler azure --check policy_ensure_asc_enforcement_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J85" s="1" t="n"/>
+      <s:c r="J85" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1484 - Domain or Tenant Policy Modification
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K85" s="1" t="n"/>
       <s:c r="L85" s="1" t="n"/>
       <s:c r="M85" s="1" t="inlineStr">
@@ -3958,7 +4244,12 @@
 prowler azure --check postgres_flexible_server_entra_admin_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J87" s="1" t="n"/>
+      <s:c r="J87" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1556.006 - Multi-Factor Authentication</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K87" s="1" t="n"/>
       <s:c r="L87" s="1" t="n"/>
       <s:c r="M87" s="1" t="inlineStr">
@@ -4025,7 +4316,12 @@
 prowler azure --check recovery_vault_backup_alerts_configured</s:t>
         </s:is>
       </s:c>
-      <s:c r="J89" s="1" t="n"/>
+      <s:c r="J89" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1490 - Inhibit System Recovery
+T1562.008 - Disable or Modify Cloud Logs</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K89" s="1" t="n"/>
       <s:c r="L89" s="1" t="n"/>
       <s:c r="M89" s="1" t="inlineStr">
@@ -4093,7 +4389,12 @@
 prowler azure --check redis_cache_ssl_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J91" s="1" t="n"/>
+      <s:c r="J91" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1040 - Network Sniffing
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K91" s="1" t="n"/>
       <s:c r="L91" s="1" t="n"/>
       <s:c r="M91" s="1" t="inlineStr">
@@ -4160,7 +4461,12 @@
 prowler azure --check resource_tags_exist</s:t>
         </s:is>
       </s:c>
-      <s:c r="J93" s="1" t="n"/>
+      <s:c r="J93" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1580 - Cloud Infrastructure Discovery
+T1082 - System Information Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K93" s="1" t="n"/>
       <s:c r="L93" s="1" t="n"/>
       <s:c r="M93" s="1" t="inlineStr">
@@ -4227,7 +4533,12 @@
 prowler azure --check search_service_managed_identity_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J95" s="1" t="n"/>
+      <s:c r="J95" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1552.005 - Cloud Instance Metadata API</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K95" s="1" t="n"/>
       <s:c r="L95" s="1" t="n"/>
       <s:c r="M95" s="1" t="inlineStr">
@@ -4274,7 +4585,12 @@
           <s:t>prowler azure --check aisearch_service_not_publicly_accessible</s:t>
         </s:is>
       </s:c>
-      <s:c r="J96" s="1" t="n"/>
+      <s:c r="J96" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1530 - Data from Cloud Storage</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K96" s="1" t="n"/>
       <s:c r="L96" s="1" t="n"/>
       <s:c r="M96" s="1" t="inlineStr">
@@ -4340,7 +4656,12 @@
           <s:t>az security assessment list --query "[?status.code=='Unhealthy'].{name:displayName, severity:metadata.severity}" -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J98" s="1" t="n"/>
+      <s:c r="J98" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1518.001 - Security Software Discovery
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K98" s="1" t="n"/>
       <s:c r="L98" s="1" t="n"/>
       <s:c r="M98" s="1" t="inlineStr">
@@ -4387,7 +4708,12 @@
           <s:t>az security alert list -o table</s:t>
         </s:is>
       </s:c>
-      <s:c r="J99" s="1" t="n"/>
+      <s:c r="J99" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.001 - Disable or Modify Tools
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K99" s="1" t="n"/>
       <s:c r="L99" s="1" t="n"/>
       <s:c r="M99" s="1" t="inlineStr">
@@ -4435,7 +4761,12 @@
 prowler azure --check iam_subscription_roles_owner_custom_not_created</s:t>
         </s:is>
       </s:c>
-      <s:c r="J100" s="1" t="n"/>
+      <s:c r="J100" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K100" s="1" t="n"/>
       <s:c r="L100" s="1" t="n"/>
       <s:c r="M100" s="1" t="inlineStr">
@@ -4502,7 +4833,12 @@
 prowler azure --check containerapp_environment_public_network_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J102" s="1" t="n"/>
+      <s:c r="J102" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K102" s="1" t="n"/>
       <s:c r="L102" s="1" t="n"/>
       <s:c r="M102" s="1" t="inlineStr">
@@ -4569,7 +4905,12 @@
 prowler azure --check sqlserver_public_network_access_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J104" s="1" t="n"/>
+      <s:c r="J104" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1530 - Data from Cloud Storage</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K104" s="1" t="n"/>
       <s:c r="L104" s="1" t="n"/>
       <s:c r="M104" s="1" t="inlineStr">
@@ -4617,7 +4958,12 @@
 prowler azure --check sqlserver_firewall_rules_allow_azure_services</s:t>
         </s:is>
       </s:c>
-      <s:c r="J105" s="1" t="n"/>
+      <s:c r="J105" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1530 - Data from Cloud Storage</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K105" s="1" t="n"/>
       <s:c r="L105" s="1" t="n"/>
       <s:c r="M105" s="1" t="inlineStr">
@@ -4665,7 +5011,12 @@
 prowler azure --check sqlserver_auditing_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J106" s="1" t="n"/>
+      <s:c r="J106" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1562.008 - Disable or Modify Cloud Logs
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K106" s="1" t="n"/>
       <s:c r="L106" s="1" t="n"/>
       <s:c r="M106" s="1" t="inlineStr">
@@ -4713,7 +5064,12 @@
 prowler azure --check sqlserver_tde_encrypted_with_cmk_or_platform_key</s:t>
         </s:is>
       </s:c>
-      <s:c r="J107" s="1" t="n"/>
+      <s:c r="J107" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1486 - Data Encrypted for Impact
+T1600 - Weaken Encryption</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K107" s="1" t="n"/>
       <s:c r="L107" s="1" t="n"/>
       <s:c r="M107" s="1" t="inlineStr">
@@ -4780,7 +5136,12 @@
 prowler azure --check consumption_budget_exists</s:t>
         </s:is>
       </s:c>
-      <s:c r="J109" s="1" t="n"/>
+      <s:c r="J109" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1580 - Cloud Infrastructure Discovery
+T1538 - Cloud Service Dashboard</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K109" s="1" t="n"/>
       <s:c r="L109" s="1" t="n"/>
       <s:c r="M109" s="1" t="inlineStr">
@@ -4828,7 +5189,12 @@
 prowler azure --check iam_subscription_roles_owner_count_check</s:t>
         </s:is>
       </s:c>
-      <s:c r="J110" s="1" t="n"/>
+      <s:c r="J110" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1087.004 - Cloud Account
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K110" s="1" t="n"/>
       <s:c r="L110" s="1" t="n"/>
       <s:c r="M110" s="1" t="inlineStr">
@@ -4876,7 +5242,12 @@
 prowler azure --check policy_ensure_not_allowed_resource_types</s:t>
         </s:is>
       </s:c>
-      <s:c r="J111" s="1" t="n"/>
+      <s:c r="J111" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1484 - Domain or Tenant Policy Modification
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K111" s="1" t="n"/>
       <s:c r="L111" s="1" t="n"/>
       <s:c r="M111" s="1" t="inlineStr">
@@ -4924,7 +5295,12 @@
 prowler azure --check iam_custom_role_subscription_owner_or_uaa</s:t>
         </s:is>
       </s:c>
-      <s:c r="J112" s="1" t="n"/>
+      <s:c r="J112" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K112" s="1" t="n"/>
       <s:c r="L112" s="1" t="n"/>
       <s:c r="M112" s="1" t="inlineStr">
@@ -4991,7 +5367,12 @@
 prowler azure --check synapse_workspace_encryption_at_rest_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J114" s="1" t="n"/>
+      <s:c r="J114" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1486 - Data Encrypted for Impact
+T1600 - Weaken Encryption</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K114" s="1" t="n"/>
       <s:c r="L114" s="1" t="n"/>
       <s:c r="M114" s="1" t="inlineStr">
@@ -5058,7 +5439,12 @@
 prowler azure --check vm_ensure_using_azure_disk_encryption</s:t>
         </s:is>
       </s:c>
-      <s:c r="J116" s="1" t="n"/>
+      <s:c r="J116" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1486 - Data Encrypted for Impact
+T1600 - Weaken Encryption</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K116" s="1" t="n"/>
       <s:c r="L116" s="1" t="n"/>
       <s:c r="M116" s="1" t="inlineStr">
@@ -5106,7 +5492,12 @@
 prowler azure --check vm_scaleset_public_ip_disabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J117" s="1" t="n"/>
+      <s:c r="J117" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1190 - Exploit Public-Facing Application
+T1580 - Cloud Infrastructure Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K117" s="1" t="n"/>
       <s:c r="L117" s="1" t="n"/>
       <s:c r="M117" s="1" t="inlineStr">
@@ -5154,7 +5545,12 @@
 prowler azure --check vm_backup_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J118" s="1" t="n"/>
+      <s:c r="J118" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1490 - Inhibit System Recovery
+T1485 - Data Destruction</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K118" s="1" t="n"/>
       <s:c r="L118" s="1" t="n"/>
       <s:c r="M118" s="1" t="inlineStr">
@@ -5202,7 +5598,12 @@
 prowler azure --check vm_ensure_jit_access_enabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J119" s="1" t="n"/>
+      <s:c r="J119" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1021.001 - Remote Desktop Protocol</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K119" s="1" t="n"/>
       <s:c r="L119" s="1" t="n"/>
       <s:c r="M119" s="1" t="inlineStr">
@@ -5270,7 +5671,13 @@
 roadrecon gui</s:t>
         </s:is>
       </s:c>
-      <s:c r="J121" s="1" t="n"/>
+      <s:c r="J121" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1087.004 - Cloud Account
+T1580 - Cloud Infrastructure Discovery
+T1526 - Cloud Service Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K121" s="1" t="n"/>
       <s:c r="L121" s="1" t="n"/>
       <s:c r="M121" s="1" t="inlineStr">
@@ -5318,7 +5725,13 @@
 azurehound start -o azurehound.zip</s:t>
         </s:is>
       </s:c>
-      <s:c r="J122" s="1" t="n"/>
+      <s:c r="J122" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1087.004 - Cloud Account
+T1580 - Cloud Infrastructure Discovery
+T1526 - Cloud Service Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K122" s="1" t="n"/>
       <s:c r="L122" s="1" t="n"/>
       <s:c r="M122" s="1" t="n"/>
@@ -5361,7 +5774,12 @@
           <s:t># AZ - Shortest paths to Global Administrator</s:t>
         </s:is>
       </s:c>
-      <s:c r="J123" s="1" t="n"/>
+      <s:c r="J123" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K123" s="1" t="n"/>
       <s:c r="L123" s="1" t="n"/>
       <s:c r="M123" s="1" t="n"/>
@@ -5404,7 +5822,12 @@
           <s:t>az role assignment list --scope /subscriptions/&lt;subscription-id&gt;</s:t>
         </s:is>
       </s:c>
-      <s:c r="J124" s="1" t="n"/>
+      <s:c r="J124" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K124" s="1" t="n"/>
       <s:c r="L124" s="1" t="n"/>
       <s:c r="M124" s="1" t="n"/>
@@ -5447,7 +5870,12 @@
           <s:t>roadrecon gui</s:t>
         </s:is>
       </s:c>
-      <s:c r="J125" s="1" t="n"/>
+      <s:c r="J125" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1528 - Steal Application Access Token
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K125" s="1" t="n"/>
       <s:c r="L125" s="1" t="n"/>
       <s:c r="M125" s="1" t="n"/>
@@ -5490,7 +5918,13 @@
           <s:t>roadrecon gui</s:t>
         </s:is>
       </s:c>
-      <s:c r="J126" s="1" t="n"/>
+      <s:c r="J126" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1098.003 - Additional Cloud Roles
+T1528 - Steal Application Access Token</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K126" s="1" t="n"/>
       <s:c r="L126" s="1" t="n"/>
       <s:c r="M126" s="1" t="n"/>
@@ -5533,7 +5967,13 @@
           <s:t>az role assignment list --assignee &lt;sp-object-id&gt; --all</s:t>
         </s:is>
       </s:c>
-      <s:c r="J127" s="1" t="n"/>
+      <s:c r="J127" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1078.004 - Cloud Accounts
+T1552.005 - Cloud Instance Metadata API
+T1098.003 - Additional Cloud Roles</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K127" s="1" t="n"/>
       <s:c r="L127" s="1" t="n"/>
       <s:c r="M127" s="1" t="n"/>
@@ -5576,7 +6016,13 @@
           <s:t>az role assignment list --assignee &lt;current-user-upn&gt; --all</s:t>
         </s:is>
       </s:c>
-      <s:c r="J128" s="1" t="n"/>
+      <s:c r="J128" s="1" t="inlineStr">
+        <s:is>
+          <s:t>T1098.003 - Additional Cloud Roles
+T1078.004 - Cloud Accounts
+T1651 - Cloud Administration Command</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K128" s="1" t="n"/>
       <s:c r="L128" s="1" t="n"/>
       <s:c r="M128" s="1" t="n"/>
